--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -475,7 +475,8 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,20 +537,25 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>stop_check</t>
+          <t>timeout_message</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>timeout_reminder</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>publish</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>encrypt</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>widgets</t>
         </is>
@@ -587,24 +593,25 @@
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -641,24 +648,25 @@
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -691,24 +699,25 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -746,24 +755,25 @@
           <t>error_numeric</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -796,24 +806,25 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -850,13 +861,14 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -895,13 +907,14 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -940,13 +953,14 @@
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -985,13 +999,14 @@
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1030,13 +1045,14 @@
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1071,13 +1087,14 @@
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1320,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1393,22 +1410,34 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>stop_words</t>
+          <t>timeout_nudge</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>stop, quit, unsubscribe, cancel, end</t>
+          <t>Just checking in: here is the question again whenever you have a moment. If you would rather stop, reply STOP and we will not message you again.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>stop_words</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>stop, quit, unsubscribe, cancel, end</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>unsolicited</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Thanks for your message. Nothing further is needed.</t>
         </is>
@@ -1425,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1531,34 +1560,58 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>preloads</t>
+          <t>stop_words</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>caseid, name, sent_at</t>
+          <t>opening_and_reminders</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>flow_name:en</t>
+          <t>reminder_after</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>my_survey</t>
+          <t>84600</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>preloads</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>caseid, name, sent_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>flow_name:en</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>my_survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>description:en</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>One line saying what this round is for</t>
         </is>
@@ -1575,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1844,16 +1897,16 @@
       <c r="A46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>stop_check - default yes, and it should stay yes</t>
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>timeout_reminder - default yes. Send the no-reply reminder.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Routes a mid-survey STOP before the reply is treated as an answer. Twilio's own opt-out handling covers the carrier keywords for SMS; inside a WhatsApp session a STOP is an ordinary message and nothing looks at it unless the flow does. Without this, saying stop stores 'stop' as the answer and the next question goes out anyway.</t>
+          <t xml:space="preserve">  When nobody replies for the settings' reminder_after (23h30 unless you change it), the person gets the reminder and the same question again. Then the usual timeout runs; if there is still nothing, they are marked as not replying.</t>
         </is>
       </c>
     </row>
@@ -1861,21 +1914,38 @@
       <c r="A49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>timeout_message - this question's own reminder text</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A key from the messages sheet. Blank uses timeout_nudge. A reminder goes to somebody who has gone quiet, so say they can reply STOP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>publish - default yes. Whether the answer reaches the warehouse.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>encrypt - default no. Encrypt this field before it is stored.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  For direct identifiers only - a name, a phone number.</t>
         </is>
@@ -2044,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,7 +2143,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Keys this instrument uses: error_option, error_option_labels, error_numeric, list_button, stop_words, unsolicited</t>
+          <t>Keys this instrument uses: error_option, error_option_labels, error_numeric, list_button, timeout_nudge, stop_words, unsolicited</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2173,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>stop_words - comma-separated. Include the English words even in a non-English instrument: people type STOP whatever language they are answering in.</t>
+          <t>stop_words - comma-separated. STOP is always understood, in every language, and capitals do not matter (stop, Stop, STOP). Where they are listened for is the settings' stop_words: by default the opening (opener, consent, first question) and any reply to a reminder. Mid-survey a person who has had enough simply stops answering.</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2183,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>list_button - the up-to-20-character button that opens a list.</t>
+          <t>timeout_nudge - the no-reply reminder, sent with the question again after the settings' reminder_after (23h30 by default, the last moment WhatsApp still allows free text). Tell people they can reply STOP.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2193,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>unsolicited - sent to somebody who writes to the number without having been launched into the survey. In practice that is mostly people being polite after finishing, and re-sending the opener to them would restart the whole survey.</t>
+          <t>list_button - the up-to-20-character button that opens a list.</t>
         </is>
       </c>
     </row>
@@ -2132,6 +2202,16 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>unsolicited - sent to somebody who writes to the number without having been launched into the survey. In practice that is mostly people being polite after finishing, and re-sending the opener to them would restart the whole survey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>{button} in a nudge is filled in with the list button's text, so a nudge cannot name a button that is not on screen.</t>
         </is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,8 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,20 +543,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>variables</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>timeout_reminder</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>publish</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>encrypt</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>widgets</t>
         </is>
@@ -596,20 +602,25 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr">
         <is>
+          <t>1=name</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -649,22 +660,23 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -700,22 +712,23 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -756,22 +769,23 @@
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -807,22 +821,23 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -862,13 +877,14 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -908,13 +924,14 @@
       <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -954,13 +971,14 @@
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1000,13 +1018,14 @@
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1045,14 +1064,19 @@
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>1=name</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1088,13 +1112,14 @@
       <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1180,7 +1205,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Yes, I will take part</t>
+          <t>Yes, I'll take part</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -1454,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1524,94 +1549,82 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>functions_service</t>
+          <t>default_timeout</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>rtt-survey</t>
+          <t>3600</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>default_timeout</t>
+          <t>default_retries</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>default_retries</t>
+          <t>stop_words</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>opening_and_reminders</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>stop_words</t>
+          <t>reminder_after</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>opening_and_reminders</t>
+          <t>84600</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>reminder_after</t>
+          <t>preloads</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>84600</t>
+          <t>caseid, name, sent_at</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>preloads</t>
+          <t>flow_name:en</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>caseid, name, sent_at</t>
+          <t>my_survey</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>flow_name:en</t>
+          <t>description:en</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>my_survey</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>description:en</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>One line saying what this round is for</t>
         </is>
@@ -1628,7 +1641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A55"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1916,14 +1929,14 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>timeout_message - this question's own reminder text</t>
+          <t>variables - what fills each {{n}} of the approved message in template</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A key from the messages sheet. Blank uses timeout_nudge. A reminder goes to somebody who has gone quiet, so say they can reply STOP.</t>
+          <t xml:space="preserve">  placeholder=column pairs from the preloads, separated by ;, e.g. 1=name. Every placeholder the message has must be filled: an empty one fails the send. The builder lists them when you pick the message.</t>
         </is>
       </c>
     </row>
@@ -1931,21 +1944,38 @@
       <c r="A52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>timeout_message - this question's own reminder text</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A key from the messages sheet. Blank uses timeout_nudge. A reminder goes to somebody who has gone quiet, so say they can reply STOP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>publish - default yes. Whether the answer reaches the warehouse.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>encrypt - default no. Encrypt this field before it is stored.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  For direct identifiers only - a name, a phone number.</t>
         </is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,9 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,30 +540,40 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>maximum</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>timeout_message</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>timeout_reminder</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>publish</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>encrypt</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>widgets</t>
         </is>
@@ -600,27 +612,29 @@
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>1=name</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -661,22 +675,24 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -713,22 +729,24 @@
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -770,22 +788,24 @@
       </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -822,22 +842,24 @@
       <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -878,13 +900,15 @@
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -925,13 +949,15 @@
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -972,13 +998,15 @@
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1019,13 +1047,15 @@
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1064,19 +1094,21 @@
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>1=name</t>
-        </is>
-      </c>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>1=name</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1113,13 +1145,15 @@
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1362,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1423,46 +1457,58 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>list_button</t>
+          <t>error_range</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Choose an answer</t>
+          <t>Please reply with a number {range}.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>timeout_nudge</t>
+          <t>list_button</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Just checking in: here is the question again whenever you have a moment. If you would rather stop, reply STOP and we will not message you again.</t>
+          <t>Choose an answer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>stop_words</t>
+          <t>timeout_nudge</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>stop, quit, unsubscribe, cancel, end</t>
+          <t>Just checking in: here is the question again whenever you have a moment. If you would rather stop, reply STOP and we will not message you again.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>stop_words</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>stop, quit, unsubscribe, cancel, end</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>unsolicited</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Thanks for your message. Nothing further is needed.</t>
         </is>
@@ -1641,7 +1687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1841,141 +1887,165 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Compare with =, != and, for numbers, &gt; and &lt;. Join comparisons with and, or with or, not both: ${Q2}&gt;0 and ${arm}='2'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  On a `begin group` row it branches the instrument. On a `close` row it picks which closing an outcome gets.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>retries - how many times to re-ask a reply that does not validate</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Blank uses 2. Only meaningful where a reply can fail, so a select or a constrained number - `text` cannot fail. Re-asking somebody who cannot answer is badgering a volunteer, so this is an ethical setting as much as a technical one.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr"/>
-    </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>constraint - the regex a reply must match, for integer and decimal</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Blank uses the default for the type. Whatever you write here is RUN against real replies when you check the spec, not merely read.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>minimum, maximum - the smallest and largest number it takes, both included</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  For integer and decimal. 0 and 7 for days a week: 15 is asked again with the error_range message. Leave one blank to leave that side open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>constraint_message - which nudge to send when a reply does not validate</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  A key from the messages sheet. Blank picks a sensible one.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>timeout - seconds to wait for a reply. Blank uses 3600.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>timeout_reminder - default yes. Send the no-reply reminder.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  When nobody replies for the settings' reminder_after (23h30 unless you change it), the person gets the reminder and the same question again. Then the usual timeout runs; if there is still nothing, they are marked as not replying.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>variables - what fills each {{n}} of the approved message in template</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  placeholder=column pairs from the preloads, separated by ;, e.g. 1=name. Every placeholder the message has must be filled: an empty one fails the send. The builder lists them when you pick the message.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>timeout_message - this question's own reminder text</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A key from the messages sheet. Blank uses timeout_nudge. A reminder goes to somebody who has gone quiet, so say they can reply STOP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>publish - default yes. Whether the answer reaches the warehouse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>encrypt - default no. Encrypt this field before it is stored.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A key from the messages sheet. Blank uses timeout_nudge. A reminder goes to somebody who has gone quiet, so say they can reply STOP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>publish - default yes. Whether the answer reaches the warehouse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>encrypt - default no. Encrypt this field before it is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  For direct identifiers only - a name, a phone number.</t>
         </is>
@@ -2173,7 +2243,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Keys this instrument uses: error_option, error_option_labels, error_numeric, list_button, timeout_nudge, stop_words, unsolicited</t>
+          <t>Keys this instrument uses: error_option, error_option_labels, error_numeric, error_range, list_button, timeout_nudge, stop_words, unsolicited</t>
         </is>
       </c>
     </row>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1643,34 +1643,42 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>preloads</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>caseid, name, sent_at</t>
-        </is>
-      </c>
+          <t>publish_table</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>flow_name:en</t>
+          <t>preloads</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>my_survey</t>
+          <t>caseid, name, sent_at</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>flow_name:en</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>my_survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>description:en</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>One line saying what this round is for</t>
         </is>
